--- a/Shared/XLS/Consumable.xlsx
+++ b/Shared/XLS/Consumable.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -97,14 +97,6 @@
   </si>
   <si>
     <t>LinkedSkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_USE_POSTION_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_USE_SCROLL_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -590,7 +582,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -616,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -695,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -733,7 +725,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>14</v>
@@ -750,9 +742,7 @@
       <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
     </row>
@@ -766,9 +756,7 @@
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>

--- a/Shared/XLS/Consumable.xlsx
+++ b/Shared/XLS/Consumable.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="#Enum" sheetId="1" r:id="rId1"/>
+    <sheet name="#Enum" sheetId="7" r:id="rId1"/>
     <sheet name="#Consumable" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
@@ -31,20 +31,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillPoint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectParam_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CooldownGroup</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooldown</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -52,63 +84,43 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>!float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>!string</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>포션1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Potion</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스크롤1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Scroll</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>상자1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemBox</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ConsumableType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ConsumableType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LinkedRewardIDs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LinkedSkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ConsumableType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consumable</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
+    <t>ConsumeEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ConsumeEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Item_HealSmall</t>
+  </si>
+  <si>
+    <t>SkillPoint_Item</t>
+  </si>
+  <si>
+    <t>Skill_Item_HealLarge</t>
+  </si>
+  <si>
+    <t>Skill_Item_AtkBuff</t>
+  </si>
+  <si>
+    <t>스킬 사용</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬포인트 획득</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 보상</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -116,7 +128,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,32 +160,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -186,14 +198,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -224,6 +236,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -247,59 +274,49 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -590,216 +607,231 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.75" style="9" customWidth="1"/>
+    <col min="4" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="B8"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="B9"/>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="B12"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="B13"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="B15"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="B16"/>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18"/>
+    <row r="1" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="8"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="9"/>
-    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.875" customWidth="1"/>
-    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="11" customFormat="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>1030100001</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>1030100002</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>1030100003</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>1030200001</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>1030200002</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>1001</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9">
+        <v>1030300001</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="B4" s="1">
-        <v>70001</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="B5" s="1">
-        <v>70002</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="10"/>
-      <c r="B6" s="1">
-        <v>70003</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="5">
-        <v>101</v>
-      </c>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="10"/>
-      <c r="B7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="10"/>
-      <c r="B8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="10"/>
-      <c r="B9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
